--- a/Luban/Data/__tables__.xlsx
+++ b/Luban/Data/__tables__.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.375" customWidth="1" style="2" min="2" max="2"/>
@@ -580,12 +580,12 @@
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t>demo.TbItem</t>
+          <t>TbItemConfig</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>demo.Item</t>
+          <t>ItemConfig</t>
         </is>
       </c>
       <c r="D4" s="0" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>#demo.item.xlsx</t>
+          <t>#itemconfig.xlsx</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">
@@ -603,14 +603,21 @@
           <t>id</t>
         </is>
       </c>
+      <c r="G4" s="0" t="inlineStr"/>
+      <c r="H4" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
       <c r="I4" s="0" t="inlineStr">
         <is>
-          <t>demo 道具表</t>
-        </is>
-      </c>
+          <t>道具表（类型 + 刷新/拾取/携带/使用 + 各类型效果数值）</t>
+        </is>
+      </c>
+      <c r="J4" s="0" t="inlineStr"/>
       <c r="K4" s="0" t="inlineStr">
         <is>
-          <t>demo_tbitem</t>
+          <t>itemconfig</t>
         </is>
       </c>
     </row>
@@ -783,6 +790,55 @@
         </is>
       </c>
       <c r="J8" s="0" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>TbMovementConfig</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>MovementConfig</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>#movementconfig.xlsx</t>
+        </is>
+      </c>
+      <c r="F9" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G9" s="0" t="inlineStr"/>
+      <c r="H9" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="I9" s="0" t="inlineStr">
+        <is>
+          <t>移动数值表（单行：走跑冲/加减速/滑铲/空中/跳跃/钩爪/闪现；消费点 MovementConfig 静态类）</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>movementconfig</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Luban/Data/__tables__.xlsx
+++ b/Luban/Data/__tables__.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.375" customWidth="1" style="2" min="2" max="2"/>
@@ -834,9 +834,56 @@
         </is>
       </c>
       <c r="J9" s="0" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
+      <c r="K9" s="0" t="inlineStr">
         <is>
           <t>movementconfig</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>TbWeapon</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>#weapon.xlsx</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>武器表（射速/弹药/换弹/伤害/射程/散布；消费点 WeaponConfig 静态类）</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>weapon</t>
         </is>
       </c>
     </row>

--- a/Luban/Data/__tables__.xlsx
+++ b/Luban/Data/__tables__.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -333,7 +333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.375" customWidth="1" style="2" min="2" max="2"/>
@@ -902,6 +902,51 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>TbText</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>TextEntry</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>#ltext.xlsx</t>
+        </is>
+      </c>
+      <c r="F13" s="0" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="G13" s="0" t="n"/>
+      <c r="H13" s="0" t="n"/>
+      <c r="I13" s="0" t="inlineStr">
+        <is>
+          <t>LText 文案表（key→zh/en；BindLocale 数据源——表现层，进 DATA_EXCLUDE_NAMES；表源 #ltext.xlsx）</t>
+        </is>
+      </c>
+      <c r="J13" s="0" t="n"/>
+      <c r="K13" s="0" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Luban/Data/__tables__.xlsx
+++ b/Luban/Data/__tables__.xlsx
@@ -333,7 +333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.375" customWidth="1" style="2" min="2" max="2"/>
@@ -947,6 +947,55 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>TbCrosshair</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>CrosshairFeel</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>#crosshair.xlsx</t>
+        </is>
+      </c>
+      <c r="F14" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G14" s="0" t="inlineStr"/>
+      <c r="H14" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I14" s="0" t="inlineStr">
+        <is>
+          <t>准心调参表（表现域：静态满张/连发张开/后坐——按武器一行；纯 View 不进判定面摘要）</t>
+        </is>
+      </c>
+      <c r="J14" s="0" t="inlineStr"/>
+      <c r="K14" s="0" t="inlineStr">
+        <is>
+          <t>crosshair</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
